--- a/models/holdings/NOW_Valuation.xlsx
+++ b/models/holdings/NOW_Valuation.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="128">
   <si>
     <t xml:space="preserve">ServiceNow (NOW): valuation summary</t>
   </si>
@@ -79,30 +79,6 @@
   </si>
   <si>
     <t xml:space="preserve">Sell if subscription revenue or current remaining performance obligations grow less than 15%.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Levels follow the rules on the positions page and are reset when the model changes.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Notes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Base value is what the business is worth if the base case plays out and you want to earn the discount rate. Implied return is what the base case earns at today's price.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DCF: five explicit years, then five years fading growth, margin and reinvestment to terminal levels. FCF = operating income x (1 - tax) - net reinvestment - working capital x revenue change. Mid-year discounting from October 2026.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Margins are after stock-based pay. For ServiceNow that is about 19% today, not the 31.5% non-GAAP figure, which is the main reason its value is lower than a multiple of adjusted earnings suggests.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Banks: tangible book plus the present value of returns above the cost of equity (residual income). TMC: probability-weighted, from the company's 2025 study with analyst haircuts.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Discount rates use a 5.31% risk-free rate and a 5% equity risk premium, the same as the earlier journal models. At these rates most quality stocks look fully priced; the implied return column shows by how much.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Price and data dates are on the model sheet. Company data: Stock Analysis, company filings and releases. Research for my own records, not investment advice.</t>
   </si>
   <si>
     <t xml:space="preserve">ServiceNow (NOW): 10-year scenario DCF</t>
@@ -436,7 +412,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="10">
+  <numFmts count="9">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="\$#,##0.00;&quot;($&quot;#,##0.00\);\-"/>
     <numFmt numFmtId="166" formatCode="0.0%;\(0.0%\);\-"/>
@@ -444,9 +420,8 @@
     <numFmt numFmtId="168" formatCode="0.000"/>
     <numFmt numFmtId="169" formatCode="#,##0.0;\(#,##0.0\);\-"/>
     <numFmt numFmtId="170" formatCode="0"/>
-    <numFmt numFmtId="171" formatCode="General"/>
-    <numFmt numFmtId="172" formatCode="0.00"/>
-    <numFmt numFmtId="173" formatCode="#,##0.0"/>
+    <numFmt numFmtId="171" formatCode="0.00"/>
+    <numFmt numFmtId="172" formatCode="#,##0.0"/>
   </numFmts>
   <fonts count="10">
     <font>
@@ -575,11 +550,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -587,51 +566,51 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="169" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="170" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -639,63 +618,59 @@
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="171" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="171" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="172" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="172" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="173" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -954,170 +929,142 @@
   <dimension ref="A1:J21"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="3" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="3" style="1" width="13"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="H4" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="I4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="J4" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="4" t="n">
+      <c r="C5" s="5" t="n">
         <f aca="false">NOW!B4</f>
         <v>156.84</v>
       </c>
-      <c r="D5" s="5" t="n">
+      <c r="D5" s="6" t="n">
         <f aca="false">NOW!B10</f>
         <v>0.095</v>
       </c>
-      <c r="E5" s="4" t="n">
+      <c r="E5" s="5" t="n">
         <f aca="false">NOW!B75</f>
         <v>58.8528253261598</v>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="F5" s="5" t="n">
         <f aca="false">NOW!B76</f>
         <v>103.660517846071</v>
       </c>
-      <c r="G5" s="4" t="n">
+      <c r="G5" s="5" t="n">
         <f aca="false">NOW!B77</f>
         <v>151.933982066243</v>
       </c>
-      <c r="H5" s="6" t="n">
+      <c r="H5" s="7" t="n">
         <f aca="false">F5/C5-1</f>
         <v>-0.339068363644023</v>
       </c>
-      <c r="I5" s="5" t="n">
+      <c r="I5" s="6" t="n">
         <f aca="false">NOW!B86</f>
         <v>0.0779756053156868</v>
       </c>
-      <c r="J5" s="7" t="n">
+      <c r="J5" s="8" t="n">
         <f aca="false">IF(F5&lt;10,ROUND(F5*4,0)/4,IF(F5&lt;100,ROUND(F5,0),ROUND(F5/5,0)*5))</f>
         <v>105</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="8" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="9" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="7" t="n">
+      <c r="C9" s="8" t="n">
         <v>105</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="7" t="n">
+      <c r="C10" s="8" t="n">
         <v>150</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="7" t="n">
+      <c r="C11" s="8" t="n">
         <v>81</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="0" t="s">
+      <c r="C12" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
-        <v>26</v>
-      </c>
-    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="3"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="9"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1137,253 +1084,253 @@
   <dimension ref="A1:L86"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="4" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="4" style="1" width="11"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="10" t="n">
+        <v>156.84</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" s="12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="B7" s="13" t="n">
+        <v>-1.75</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B4" s="9" t="n">
-        <v>156.84</v>
-      </c>
-      <c r="C4" s="2" t="s">
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="B8" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="10" t="s">
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="B9" s="14" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B6" s="11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="B7" s="12" t="n">
-        <v>-1.75</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
-        <v>38</v>
-      </c>
-      <c r="B8" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
-        <v>40</v>
-      </c>
-      <c r="B9" s="13" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
-        <v>42</v>
-      </c>
-      <c r="B10" s="14" t="n">
+      <c r="B10" s="15" t="n">
         <f aca="false">WACC!B29</f>
         <v>0.095</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B11" s="14" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B12" s="13" t="n">
+        <v>16.22</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="B15" s="17" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="C15" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="B11" s="13" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="C11" s="2" t="s">
+      <c r="D15" s="17" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="E15" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="B12" s="12" t="n">
-        <v>16.22</v>
-      </c>
-      <c r="C12" s="2" t="s">
+      <c r="F15" s="17" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+      <c r="G15" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="B13" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="C13" s="2" t="s">
+      <c r="H15" s="17" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="8" t="s">
+      <c r="I15" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="B15" s="16" t="s">
+      <c r="J15" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="C15" s="16" t="s">
+      <c r="K15" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="D15" s="16" t="s">
+      <c r="L15" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="E15" s="16" t="s">
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="F15" s="16" t="s">
-        <v>55</v>
-      </c>
-      <c r="G15" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="H15" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="I15" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="J15" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="K15" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="L15" s="8" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
-        <v>62</v>
-      </c>
-      <c r="B16" s="10" t="n">
+      <c r="B16" s="11" t="n">
         <v>0.5</v>
       </c>
-      <c r="C16" s="17" t="n">
+      <c r="C16" s="1" t="n">
         <f aca="false">B16+1</f>
         <v>1.5</v>
       </c>
-      <c r="D16" s="17" t="n">
+      <c r="D16" s="1" t="n">
         <f aca="false">C16+1</f>
         <v>2.5</v>
       </c>
-      <c r="E16" s="17" t="n">
+      <c r="E16" s="1" t="n">
         <f aca="false">D16+1</f>
         <v>3.5</v>
       </c>
-      <c r="F16" s="17" t="n">
+      <c r="F16" s="1" t="n">
         <f aca="false">E16+1</f>
         <v>4.5</v>
       </c>
-      <c r="G16" s="17" t="n">
+      <c r="G16" s="1" t="n">
         <f aca="false">F16+1</f>
         <v>5.5</v>
       </c>
-      <c r="H16" s="17" t="n">
+      <c r="H16" s="1" t="n">
         <f aca="false">G16+1</f>
         <v>6.5</v>
       </c>
-      <c r="I16" s="17" t="n">
+      <c r="I16" s="1" t="n">
         <f aca="false">H16+1</f>
         <v>7.5</v>
       </c>
-      <c r="J16" s="17" t="n">
+      <c r="J16" s="1" t="n">
         <f aca="false">I16+1</f>
         <v>8.5</v>
       </c>
-      <c r="K16" s="17" t="n">
+      <c r="K16" s="1" t="n">
         <f aca="false">J16+1</f>
         <v>9.5</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
-        <v>63</v>
-      </c>
-      <c r="B17" s="0" t="n">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B17" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="C17" s="0" t="n">
+      <c r="C17" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="D17" s="0" t="n">
+      <c r="D17" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="E17" s="0" t="n">
+      <c r="E17" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="F17" s="0" t="n">
+      <c r="F17" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="G17" s="0" t="n">
+      <c r="G17" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="H17" s="0" t="n">
+      <c r="H17" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="I17" s="0" t="n">
+      <c r="I17" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="J17" s="0" t="n">
+      <c r="J17" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="K17" s="0" t="n">
+      <c r="K17" s="1" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="18" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="B19" s="19"/>
       <c r="C19" s="19"/>
@@ -1397,23 +1344,23 @@
       <c r="K19" s="19"/>
       <c r="L19" s="19"/>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
-        <v>65</v>
-      </c>
-      <c r="B20" s="12" t="n">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B20" s="13" t="n">
         <v>18.3</v>
       </c>
-      <c r="C20" s="12" t="n">
+      <c r="C20" s="13" t="n">
         <v>20.3</v>
       </c>
-      <c r="D20" s="12" t="n">
+      <c r="D20" s="13" t="n">
         <v>22.2</v>
       </c>
-      <c r="E20" s="12" t="n">
+      <c r="E20" s="13" t="n">
         <v>24</v>
       </c>
-      <c r="F20" s="12" t="n">
+      <c r="F20" s="13" t="n">
         <v>25.7</v>
       </c>
       <c r="G20" s="20" t="n">
@@ -1441,47 +1388,47 @@
         <v>33.8329230548294</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
-        <v>66</v>
-      </c>
-      <c r="B21" s="6" t="n">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B21" s="7" t="n">
         <f aca="false">B20/$B$12-1</f>
         <v>0.128236744759556</v>
       </c>
-      <c r="C21" s="6" t="n">
+      <c r="C21" s="7" t="n">
         <f aca="false">C20/B20-1</f>
         <v>0.109289617486339</v>
       </c>
-      <c r="D21" s="6" t="n">
+      <c r="D21" s="7" t="n">
         <f aca="false">D20/C20-1</f>
         <v>0.0935960591133005</v>
       </c>
-      <c r="E21" s="6" t="n">
+      <c r="E21" s="7" t="n">
         <f aca="false">E20/D20-1</f>
         <v>0.0810810810810811</v>
       </c>
-      <c r="F21" s="6" t="n">
+      <c r="F21" s="7" t="n">
         <f aca="false">F20/E20-1</f>
         <v>0.0708333333333333</v>
       </c>
-      <c r="G21" s="6" t="n">
+      <c r="G21" s="7" t="n">
         <f aca="false">G20/F20-1</f>
         <v>0.0636666666666665</v>
       </c>
-      <c r="H21" s="6" t="n">
+      <c r="H21" s="7" t="n">
         <f aca="false">H20/G20-1</f>
         <v>0.0565</v>
       </c>
-      <c r="I21" s="6" t="n">
+      <c r="I21" s="7" t="n">
         <f aca="false">I20/H20-1</f>
         <v>0.0493333333333332</v>
       </c>
-      <c r="J21" s="6" t="n">
+      <c r="J21" s="7" t="n">
         <f aca="false">J20/I20-1</f>
         <v>0.0421666666666667</v>
       </c>
-      <c r="K21" s="6" t="n">
+      <c r="K21" s="7" t="n">
         <f aca="false">K20/J20-1</f>
         <v>0.0349999999999999</v>
       </c>
@@ -1489,9 +1436,9 @@
         <v>0.035</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
-        <v>67</v>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="B22" s="22" t="n">
         <v>0.17</v>
@@ -1508,23 +1455,23 @@
       <c r="F22" s="22" t="n">
         <v>0.21</v>
       </c>
-      <c r="G22" s="6" t="n">
+      <c r="G22" s="7" t="n">
         <f aca="false">$F22+($L22-$F22)*G$17/5</f>
         <v>0.214</v>
       </c>
-      <c r="H22" s="6" t="n">
+      <c r="H22" s="7" t="n">
         <f aca="false">$F22+($L22-$F22)*H$17/5</f>
         <v>0.218</v>
       </c>
-      <c r="I22" s="6" t="n">
+      <c r="I22" s="7" t="n">
         <f aca="false">$F22+($L22-$F22)*I$17/5</f>
         <v>0.222</v>
       </c>
-      <c r="J22" s="6" t="n">
+      <c r="J22" s="7" t="n">
         <f aca="false">$F22+($L22-$F22)*J$17/5</f>
         <v>0.226</v>
       </c>
-      <c r="K22" s="6" t="n">
+      <c r="K22" s="7" t="n">
         <f aca="false">$F22+($L22-$F22)*K$17/5</f>
         <v>0.23</v>
       </c>
@@ -1532,9 +1479,9 @@
         <v>0.23</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
-        <v>68</v>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="s">
+        <v>60</v>
       </c>
       <c r="B23" s="20" t="n">
         <f aca="false">B20*B22</f>
@@ -1581,9 +1528,9 @@
         <v>7.78157230261077</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
-        <v>69</v>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="s">
+        <v>61</v>
       </c>
       <c r="B24" s="20" t="n">
         <f aca="false">B23*(1-$B$9)</f>
@@ -1630,9 +1577,9 @@
         <v>6.22525784208862</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
-        <v>70</v>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1" t="s">
+        <v>62</v>
       </c>
       <c r="B25" s="22" t="n">
         <v>0.03</v>
@@ -1649,23 +1596,23 @@
       <c r="F25" s="22" t="n">
         <v>0.03</v>
       </c>
-      <c r="G25" s="6" t="n">
+      <c r="G25" s="7" t="n">
         <f aca="false">$F25+($L25-$F25)*G$17/5</f>
         <v>0.028</v>
       </c>
-      <c r="H25" s="6" t="n">
+      <c r="H25" s="7" t="n">
         <f aca="false">$F25+($L25-$F25)*H$17/5</f>
         <v>0.026</v>
       </c>
-      <c r="I25" s="6" t="n">
+      <c r="I25" s="7" t="n">
         <f aca="false">$F25+($L25-$F25)*I$17/5</f>
         <v>0.024</v>
       </c>
-      <c r="J25" s="6" t="n">
+      <c r="J25" s="7" t="n">
         <f aca="false">$F25+($L25-$F25)*J$17/5</f>
         <v>0.022</v>
       </c>
-      <c r="K25" s="6" t="n">
+      <c r="K25" s="7" t="n">
         <f aca="false">$F25+($L25-$F25)*K$17/5</f>
         <v>0.02</v>
       </c>
@@ -1673,9 +1620,9 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
-        <v>71</v>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1" t="s">
+        <v>63</v>
       </c>
       <c r="B26" s="20" t="n">
         <f aca="false">B20*B25</f>
@@ -1722,9 +1669,9 @@
         <v>0.676658461096589</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
-        <v>72</v>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="B27" s="20" t="n">
         <f aca="false">$B$11*(B20-$B$12)</f>
@@ -1771,9 +1718,9 @@
         <v>-0.0572054254550256</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="s">
-        <v>73</v>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="B28" s="20" t="n">
         <f aca="false">B24-B26-B27</f>
@@ -1820,9 +1767,9 @@
         <v>5.60580480644705</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="s">
-        <v>74</v>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1" t="s">
+        <v>66</v>
       </c>
       <c r="B29" s="23" t="n">
         <f aca="false">1/(1+$B$10)^B$16</f>
@@ -1865,9 +1812,9 @@
         <v>0.422246314721034</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="0" t="s">
-        <v>75</v>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="1" t="s">
+        <v>67</v>
       </c>
       <c r="B30" s="20" t="n">
         <f aca="false">B28*B29</f>
@@ -1911,58 +1858,58 @@
       </c>
       <c r="L30" s="20"/>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="0" t="s">
-        <v>76</v>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="1" t="s">
+        <v>68</v>
       </c>
       <c r="B31" s="20" t="n">
         <f aca="false">L28/($B$10-L21)</f>
         <v>93.4300801074509</v>
       </c>
-      <c r="C31" s="0" t="str">
+      <c r="C31" s="1" t="str">
         <f aca="false">IF($B$10&gt;L21,"","Discount rate must exceed terminal growth")</f>
         <v/>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="0" t="s">
-        <v>77</v>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="1" t="s">
+        <v>69</v>
       </c>
       <c r="B32" s="20" t="n">
         <f aca="false">B31/(1+$B$10)^$K$16</f>
         <v>39.4505070094622</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="0" t="s">
-        <v>78</v>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="1" t="s">
+        <v>70</v>
       </c>
       <c r="B33" s="20" t="n">
         <f aca="false">SUM(B30:K30)+B32+$B$7+$B$8</f>
         <v>60.6184100859446</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="0" t="s">
-        <v>79</v>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="1" t="s">
+        <v>71</v>
       </c>
       <c r="B34" s="24" t="n">
         <f aca="false">B33/$B$6</f>
         <v>58.8528253261598</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="0" t="s">
-        <v>80</v>
-      </c>
-      <c r="B35" s="6" t="n">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B35" s="7" t="n">
         <f aca="false">B34/$B$4-1</f>
         <v>-0.624758828575875</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="18" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="B37" s="19"/>
       <c r="C37" s="19"/>
@@ -1976,23 +1923,23 @@
       <c r="K37" s="19"/>
       <c r="L37" s="19"/>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="0" t="s">
-        <v>65</v>
-      </c>
-      <c r="B38" s="12" t="n">
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B38" s="13" t="n">
         <v>19.2</v>
       </c>
-      <c r="C38" s="12" t="n">
+      <c r="C38" s="13" t="n">
         <v>22.4</v>
       </c>
-      <c r="D38" s="12" t="n">
+      <c r="D38" s="13" t="n">
         <v>25.8</v>
       </c>
-      <c r="E38" s="12" t="n">
+      <c r="E38" s="13" t="n">
         <v>29.2</v>
       </c>
-      <c r="F38" s="12" t="n">
+      <c r="F38" s="13" t="n">
         <v>32.6</v>
       </c>
       <c r="G38" s="20" t="n">
@@ -2020,47 +1967,47 @@
         <v>47.6314906706745</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="0" t="s">
-        <v>66</v>
-      </c>
-      <c r="B39" s="6" t="n">
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B39" s="7" t="n">
         <f aca="false">B38/$B$12-1</f>
         <v>0.183723797780518</v>
       </c>
-      <c r="C39" s="6" t="n">
+      <c r="C39" s="7" t="n">
         <f aca="false">C38/B38-1</f>
         <v>0.166666666666667</v>
       </c>
-      <c r="D39" s="6" t="n">
+      <c r="D39" s="7" t="n">
         <f aca="false">D38/C38-1</f>
         <v>0.151785714285714</v>
       </c>
-      <c r="E39" s="6" t="n">
+      <c r="E39" s="7" t="n">
         <f aca="false">E38/D38-1</f>
         <v>0.131782945736434</v>
       </c>
-      <c r="F39" s="6" t="n">
+      <c r="F39" s="7" t="n">
         <f aca="false">F38/E38-1</f>
         <v>0.116438356164384</v>
       </c>
-      <c r="G39" s="6" t="n">
+      <c r="G39" s="7" t="n">
         <f aca="false">G38/F38-1</f>
         <v>0.101150684931507</v>
       </c>
-      <c r="H39" s="6" t="n">
+      <c r="H39" s="7" t="n">
         <f aca="false">H38/G38-1</f>
         <v>0.0858630136986303</v>
       </c>
-      <c r="I39" s="6" t="n">
+      <c r="I39" s="7" t="n">
         <f aca="false">I38/H38-1</f>
         <v>0.0705753424657534</v>
       </c>
-      <c r="J39" s="6" t="n">
+      <c r="J39" s="7" t="n">
         <f aca="false">J38/I38-1</f>
         <v>0.0552876712328767</v>
       </c>
-      <c r="K39" s="6" t="n">
+      <c r="K39" s="7" t="n">
         <f aca="false">K38/J38-1</f>
         <v>0.04</v>
       </c>
@@ -2068,9 +2015,9 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="0" t="s">
-        <v>67</v>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="B40" s="22" t="n">
         <v>0.19</v>
@@ -2087,23 +2034,23 @@
       <c r="F40" s="22" t="n">
         <v>0.26</v>
       </c>
-      <c r="G40" s="6" t="n">
+      <c r="G40" s="7" t="n">
         <f aca="false">$F40+($L40-$F40)*G$17/5</f>
         <v>0.262</v>
       </c>
-      <c r="H40" s="6" t="n">
+      <c r="H40" s="7" t="n">
         <f aca="false">$F40+($L40-$F40)*H$17/5</f>
         <v>0.264</v>
       </c>
-      <c r="I40" s="6" t="n">
+      <c r="I40" s="7" t="n">
         <f aca="false">$F40+($L40-$F40)*I$17/5</f>
         <v>0.266</v>
       </c>
-      <c r="J40" s="6" t="n">
+      <c r="J40" s="7" t="n">
         <f aca="false">$F40+($L40-$F40)*J$17/5</f>
         <v>0.268</v>
       </c>
-      <c r="K40" s="6" t="n">
+      <c r="K40" s="7" t="n">
         <f aca="false">$F40+($L40-$F40)*K$17/5</f>
         <v>0.27</v>
       </c>
@@ -2111,9 +2058,9 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="0" t="s">
-        <v>68</v>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="1" t="s">
+        <v>60</v>
       </c>
       <c r="B41" s="20" t="n">
         <f aca="false">B38*B40</f>
@@ -2160,9 +2107,9 @@
         <v>12.8605024810821</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="0" t="s">
-        <v>69</v>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="1" t="s">
+        <v>61</v>
       </c>
       <c r="B42" s="20" t="n">
         <f aca="false">B41*(1-$B$9)</f>
@@ -2209,9 +2156,9 @@
         <v>10.2884019848657</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="0" t="s">
-        <v>70</v>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="1" t="s">
+        <v>62</v>
       </c>
       <c r="B43" s="22" t="n">
         <v>0.03</v>
@@ -2228,23 +2175,23 @@
       <c r="F43" s="22" t="n">
         <v>0.03</v>
       </c>
-      <c r="G43" s="6" t="n">
+      <c r="G43" s="7" t="n">
         <f aca="false">$F43+($L43-$F43)*G$17/5</f>
         <v>0.028</v>
       </c>
-      <c r="H43" s="6" t="n">
+      <c r="H43" s="7" t="n">
         <f aca="false">$F43+($L43-$F43)*H$17/5</f>
         <v>0.026</v>
       </c>
-      <c r="I43" s="6" t="n">
+      <c r="I43" s="7" t="n">
         <f aca="false">$F43+($L43-$F43)*I$17/5</f>
         <v>0.024</v>
       </c>
-      <c r="J43" s="6" t="n">
+      <c r="J43" s="7" t="n">
         <f aca="false">$F43+($L43-$F43)*J$17/5</f>
         <v>0.022</v>
       </c>
-      <c r="K43" s="6" t="n">
+      <c r="K43" s="7" t="n">
         <f aca="false">$F43+($L43-$F43)*K$17/5</f>
         <v>0.02</v>
       </c>
@@ -2252,9 +2199,9 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="0" t="s">
-        <v>71</v>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="1" t="s">
+        <v>63</v>
       </c>
       <c r="B44" s="20" t="n">
         <f aca="false">B38*B43</f>
@@ -2301,9 +2248,9 @@
         <v>0.95262981341349</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="0" t="s">
-        <v>72</v>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="B45" s="20" t="n">
         <f aca="false">$B$11*(B38-$B$12)</f>
@@ -2350,9 +2297,9 @@
         <v>-0.0915990205205279</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="0" t="s">
-        <v>73</v>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="B46" s="20" t="n">
         <f aca="false">B42-B44-B45</f>
@@ -2399,9 +2346,9 @@
         <v>9.42737119197273</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="0" t="s">
-        <v>74</v>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="1" t="s">
+        <v>66</v>
       </c>
       <c r="B47" s="23" t="n">
         <f aca="false">1/(1+$B$10)^B$16</f>
@@ -2444,9 +2391,9 @@
         <v>0.422246314721034</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="0" t="s">
-        <v>75</v>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="1" t="s">
+        <v>67</v>
       </c>
       <c r="B48" s="20" t="n">
         <f aca="false">B46*B47</f>
@@ -2490,58 +2437,58 @@
       </c>
       <c r="L48" s="20"/>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="0" t="s">
-        <v>76</v>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="1" t="s">
+        <v>68</v>
       </c>
       <c r="B49" s="20" t="n">
         <f aca="false">L46/($B$10-L39)</f>
         <v>171.406748944959</v>
       </c>
-      <c r="C49" s="0" t="str">
+      <c r="C49" s="1" t="str">
         <f aca="false">IF($B$10&gt;L39,"","Discount rate must exceed terminal growth")</f>
         <v/>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="0" t="s">
-        <v>77</v>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="1" t="s">
+        <v>69</v>
       </c>
       <c r="B50" s="20" t="n">
         <f aca="false">B49/(1+$B$10)^$K$16</f>
         <v>72.3758680603224</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="0" t="s">
-        <v>78</v>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="1" t="s">
+        <v>70</v>
       </c>
       <c r="B51" s="20" t="n">
         <f aca="false">SUM(B48:K48)+B50+$B$7+$B$8</f>
         <v>106.770333381454</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="0" t="s">
-        <v>79</v>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="1" t="s">
+        <v>71</v>
       </c>
       <c r="B52" s="24" t="n">
         <f aca="false">B51/$B$6</f>
         <v>103.660517846071</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="0" t="s">
-        <v>80</v>
-      </c>
-      <c r="B53" s="6" t="n">
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B53" s="7" t="n">
         <f aca="false">B52/$B$4-1</f>
         <v>-0.339068363644023</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="18" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="B55" s="19"/>
       <c r="C55" s="19"/>
@@ -2555,23 +2502,23 @@
       <c r="K55" s="19"/>
       <c r="L55" s="19"/>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="0" t="s">
-        <v>65</v>
-      </c>
-      <c r="B56" s="12" t="n">
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B56" s="13" t="n">
         <v>19.6</v>
       </c>
-      <c r="C56" s="12" t="n">
+      <c r="C56" s="13" t="n">
         <v>23.6</v>
       </c>
-      <c r="D56" s="12" t="n">
+      <c r="D56" s="13" t="n">
         <v>28</v>
       </c>
-      <c r="E56" s="12" t="n">
+      <c r="E56" s="13" t="n">
         <v>32.7</v>
       </c>
-      <c r="F56" s="12" t="n">
+      <c r="F56" s="13" t="n">
         <v>37.6</v>
       </c>
       <c r="G56" s="20" t="n">
@@ -2599,47 +2546,47 @@
         <v>59.5005475360074</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="0" t="s">
-        <v>66</v>
-      </c>
-      <c r="B57" s="6" t="n">
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B57" s="7" t="n">
         <f aca="false">B56/$B$12-1</f>
         <v>0.208384710234279</v>
       </c>
-      <c r="C57" s="6" t="n">
+      <c r="C57" s="7" t="n">
         <f aca="false">C56/B56-1</f>
         <v>0.204081632653061</v>
       </c>
-      <c r="D57" s="6" t="n">
+      <c r="D57" s="7" t="n">
         <f aca="false">D56/C56-1</f>
         <v>0.186440677966102</v>
       </c>
-      <c r="E57" s="6" t="n">
+      <c r="E57" s="7" t="n">
         <f aca="false">E56/D56-1</f>
         <v>0.167857142857143</v>
       </c>
-      <c r="F57" s="6" t="n">
+      <c r="F57" s="7" t="n">
         <f aca="false">F56/E56-1</f>
         <v>0.149847094801223</v>
       </c>
-      <c r="G57" s="6" t="n">
+      <c r="G57" s="7" t="n">
         <f aca="false">G56/F56-1</f>
         <v>0.128877675840978</v>
       </c>
-      <c r="H57" s="6" t="n">
+      <c r="H57" s="7" t="n">
         <f aca="false">H56/G56-1</f>
         <v>0.107908256880734</v>
       </c>
-      <c r="I57" s="6" t="n">
+      <c r="I57" s="7" t="n">
         <f aca="false">I56/H56-1</f>
         <v>0.0869388379204892</v>
       </c>
-      <c r="J57" s="6" t="n">
+      <c r="J57" s="7" t="n">
         <f aca="false">J56/I56-1</f>
         <v>0.0659694189602447</v>
       </c>
-      <c r="K57" s="6" t="n">
+      <c r="K57" s="7" t="n">
         <f aca="false">K56/J56-1</f>
         <v>0.0449999999999999</v>
       </c>
@@ -2647,9 +2594,9 @@
         <v>0.045</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="0" t="s">
-        <v>67</v>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="B58" s="22" t="n">
         <v>0.2</v>
@@ -2666,23 +2613,23 @@
       <c r="F58" s="22" t="n">
         <v>0.28</v>
       </c>
-      <c r="G58" s="6" t="n">
+      <c r="G58" s="7" t="n">
         <f aca="false">$F58+($L58-$F58)*G$17/5</f>
         <v>0.284</v>
       </c>
-      <c r="H58" s="6" t="n">
+      <c r="H58" s="7" t="n">
         <f aca="false">$F58+($L58-$F58)*H$17/5</f>
         <v>0.288</v>
       </c>
-      <c r="I58" s="6" t="n">
+      <c r="I58" s="7" t="n">
         <f aca="false">$F58+($L58-$F58)*I$17/5</f>
         <v>0.292</v>
       </c>
-      <c r="J58" s="6" t="n">
+      <c r="J58" s="7" t="n">
         <f aca="false">$F58+($L58-$F58)*J$17/5</f>
         <v>0.296</v>
       </c>
-      <c r="K58" s="6" t="n">
+      <c r="K58" s="7" t="n">
         <f aca="false">$F58+($L58-$F58)*K$17/5</f>
         <v>0.3</v>
       </c>
@@ -2690,9 +2637,9 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="0" t="s">
-        <v>68</v>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="1" t="s">
+        <v>60</v>
       </c>
       <c r="B59" s="20" t="n">
         <f aca="false">B56*B58</f>
@@ -2739,9 +2686,9 @@
         <v>17.8501642608022</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="0" t="s">
-        <v>69</v>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="1" t="s">
+        <v>61</v>
       </c>
       <c r="B60" s="20" t="n">
         <f aca="false">B59*(1-$B$9)</f>
@@ -2788,9 +2735,9 @@
         <v>14.2801314086418</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="0" t="s">
-        <v>70</v>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A61" s="1" t="s">
+        <v>62</v>
       </c>
       <c r="B61" s="22" t="n">
         <v>0.03</v>
@@ -2807,23 +2754,23 @@
       <c r="F61" s="22" t="n">
         <v>0.03</v>
       </c>
-      <c r="G61" s="6" t="n">
+      <c r="G61" s="7" t="n">
         <f aca="false">$F61+($L61-$F61)*G$17/5</f>
         <v>0.028</v>
       </c>
-      <c r="H61" s="6" t="n">
+      <c r="H61" s="7" t="n">
         <f aca="false">$F61+($L61-$F61)*H$17/5</f>
         <v>0.026</v>
       </c>
-      <c r="I61" s="6" t="n">
+      <c r="I61" s="7" t="n">
         <f aca="false">$F61+($L61-$F61)*I$17/5</f>
         <v>0.024</v>
       </c>
-      <c r="J61" s="6" t="n">
+      <c r="J61" s="7" t="n">
         <f aca="false">$F61+($L61-$F61)*J$17/5</f>
         <v>0.022</v>
       </c>
-      <c r="K61" s="6" t="n">
+      <c r="K61" s="7" t="n">
         <f aca="false">$F61+($L61-$F61)*K$17/5</f>
         <v>0.02</v>
       </c>
@@ -2831,9 +2778,9 @@
         <v>0.02</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="0" t="s">
-        <v>71</v>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="1" t="s">
+        <v>63</v>
       </c>
       <c r="B62" s="20" t="n">
         <f aca="false">B56*B61</f>
@@ -2880,9 +2827,9 @@
         <v>1.19001095072015</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="0" t="s">
-        <v>72</v>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="1" t="s">
+        <v>64</v>
       </c>
       <c r="B63" s="20" t="n">
         <f aca="false">$B$11*(B56-$B$12)</f>
@@ -2929,9 +2876,9 @@
         <v>-0.128111226752169</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="0" t="s">
-        <v>73</v>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="1" t="s">
+        <v>65</v>
       </c>
       <c r="B64" s="20" t="n">
         <f aca="false">B60-B62-B63</f>
@@ -2978,9 +2925,9 @@
         <v>13.2182316846738</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="0" t="s">
-        <v>74</v>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="1" t="s">
+        <v>66</v>
       </c>
       <c r="B65" s="23" t="n">
         <f aca="false">1/(1+$B$10)^B$16</f>
@@ -3023,9 +2970,9 @@
         <v>0.422246314721034</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="0" t="s">
-        <v>75</v>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="1" t="s">
+        <v>67</v>
       </c>
       <c r="B66" s="20" t="n">
         <f aca="false">B64*B65</f>
@@ -3069,62 +3016,62 @@
       </c>
       <c r="L66" s="20"/>
     </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="0" t="s">
-        <v>76</v>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A67" s="1" t="s">
+        <v>68</v>
       </c>
       <c r="B67" s="20" t="n">
         <f aca="false">L64/($B$10-L57)</f>
         <v>264.364633693476</v>
       </c>
-      <c r="C67" s="0" t="str">
+      <c r="C67" s="1" t="str">
         <f aca="false">IF($B$10&gt;L57,"","Discount rate must exceed terminal growth")</f>
         <v/>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="0" t="s">
-        <v>77</v>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A68" s="1" t="s">
+        <v>69</v>
       </c>
       <c r="B68" s="20" t="n">
         <f aca="false">B67/(1+$B$10)^$K$16</f>
         <v>111.626992319646</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="0" t="s">
-        <v>78</v>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A69" s="1" t="s">
+        <v>70</v>
       </c>
       <c r="B69" s="20" t="n">
         <f aca="false">SUM(B66:K66)+B68+$B$7+$B$8</f>
         <v>156.492001528231</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="0" t="s">
-        <v>79</v>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A70" s="1" t="s">
+        <v>71</v>
       </c>
       <c r="B70" s="24" t="n">
         <f aca="false">B69/$B$6</f>
         <v>151.933982066243</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="0" t="s">
-        <v>80</v>
-      </c>
-      <c r="B71" s="6" t="n">
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A71" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B71" s="7" t="n">
         <f aca="false">B70/$B$4-1</f>
         <v>-0.0312803999856973</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="18" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="B74" s="19"/>
       <c r="C74" s="18" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="D74" s="19"/>
       <c r="E74" s="19"/>
@@ -3136,207 +3083,207 @@
       <c r="K74" s="19"/>
       <c r="L74" s="19"/>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="0" t="s">
-        <v>85</v>
-      </c>
-      <c r="B75" s="7" t="n">
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A75" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B75" s="8" t="n">
         <f aca="false">B34</f>
         <v>58.8528253261598</v>
       </c>
-      <c r="C75" s="6" t="n">
+      <c r="C75" s="7" t="n">
         <f aca="false">B75/$B$4-1</f>
         <v>-0.624758828575875</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="0" t="s">
-        <v>86</v>
-      </c>
-      <c r="B76" s="7" t="n">
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A76" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B76" s="8" t="n">
         <f aca="false">B52</f>
         <v>103.660517846071</v>
       </c>
-      <c r="C76" s="6" t="n">
+      <c r="C76" s="7" t="n">
         <f aca="false">B76/$B$4-1</f>
         <v>-0.339068363644023</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="0" t="s">
-        <v>87</v>
-      </c>
-      <c r="B77" s="7" t="n">
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A77" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="B77" s="8" t="n">
         <f aca="false">B70</f>
         <v>151.933982066243</v>
       </c>
-      <c r="C77" s="6" t="n">
+      <c r="C77" s="7" t="n">
         <f aca="false">B77/$B$4-1</f>
         <v>-0.0312803999856973</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="0" t="s">
-        <v>88</v>
-      </c>
-      <c r="B78" s="7" t="n">
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A78" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B78" s="8" t="n">
         <f aca="false">INDEX(B34:B70,1+($B$13-1)*18)</f>
         <v>103.660517846071</v>
       </c>
-      <c r="C78" s="6" t="n">
+      <c r="C78" s="7" t="n">
         <f aca="false">B78/$B$4-1</f>
         <v>-0.339068363644023</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="0" t="s">
-        <v>89</v>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A79" s="1" t="s">
+        <v>81</v>
       </c>
       <c r="B79" s="25" t="n">
         <f aca="false">B50/(SUM(B48:K48)+B50)</f>
         <v>0.666933705464378</v>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="8" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="0" t="s">
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A81" s="9" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A82" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B82" s="13" t="n">
+      <c r="B82" s="14" t="n">
         <v>0.05</v>
       </c>
-      <c r="C82" s="13" t="n">
+      <c r="C82" s="14" t="n">
         <v>0.06</v>
       </c>
-      <c r="D82" s="13" t="n">
+      <c r="D82" s="14" t="n">
         <v>0.07</v>
       </c>
-      <c r="E82" s="13" t="n">
+      <c r="E82" s="14" t="n">
         <v>0.08</v>
       </c>
-      <c r="F82" s="13" t="n">
+      <c r="F82" s="14" t="n">
         <v>0.09</v>
       </c>
-      <c r="G82" s="13" t="n">
+      <c r="G82" s="14" t="n">
         <v>0.1</v>
       </c>
-      <c r="H82" s="13" t="n">
+      <c r="H82" s="14" t="n">
         <v>0.11</v>
       </c>
-      <c r="I82" s="13" t="n">
+      <c r="I82" s="14" t="n">
         <v>0.12</v>
       </c>
-      <c r="J82" s="13" t="n">
+      <c r="J82" s="14" t="n">
         <v>0.13</v>
       </c>
-      <c r="K82" s="13" t="n">
+      <c r="K82" s="14" t="n">
         <v>0.14</v>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="0" t="s">
-        <v>86</v>
-      </c>
-      <c r="B83" s="7" t="n">
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A83" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B83" s="8" t="n">
         <f aca="false">IF(B82&gt;$L39,(SUMPRODUCT($B46:$K46/(1+B82)^$B$16:$K$16)+$L46/(B82-$L39)/(1+B82)^$K$16+$B$7+$B$8)/$B$6,"n/a")</f>
         <v>618.312595065672</v>
       </c>
-      <c r="C83" s="7" t="n">
+      <c r="C83" s="8" t="n">
         <f aca="false">IF(C82&gt;$L39,(SUMPRODUCT($B46:$K46/(1+C82)^$B$16:$K$16)+$L46/(C82-$L39)/(1+C82)^$K$16+$B$7+$B$8)/$B$6,"n/a")</f>
         <v>303.331295200872</v>
       </c>
-      <c r="D83" s="7" t="n">
+      <c r="D83" s="8" t="n">
         <f aca="false">IF(D82&gt;$L39,(SUMPRODUCT($B46:$K46/(1+D82)^$B$16:$K$16)+$L46/(D82-$L39)/(1+D82)^$K$16+$B$7+$B$8)/$B$6,"n/a")</f>
         <v>198.527621986931</v>
       </c>
-      <c r="E83" s="7" t="n">
+      <c r="E83" s="8" t="n">
         <f aca="false">IF(E82&gt;$L39,(SUMPRODUCT($B46:$K46/(1+E82)^$B$16:$K$16)+$L46/(E82-$L39)/(1+E82)^$K$16+$B$7+$B$8)/$B$6,"n/a")</f>
         <v>146.258709049454</v>
       </c>
-      <c r="F83" s="7" t="n">
+      <c r="F83" s="8" t="n">
         <f aca="false">IF(F82&gt;$L39,(SUMPRODUCT($B46:$K46/(1+F82)^$B$16:$K$16)+$L46/(F82-$L39)/(1+F82)^$K$16+$B$7+$B$8)/$B$6,"n/a")</f>
         <v>114.996601171465</v>
       </c>
-      <c r="G83" s="7" t="n">
+      <c r="G83" s="8" t="n">
         <f aca="false">IF(G82&gt;$L39,(SUMPRODUCT($B46:$K46/(1+G82)^$B$16:$K$16)+$L46/(G82-$L39)/(1+G82)^$K$16+$B$7+$B$8)/$B$6,"n/a")</f>
         <v>94.2324479617951</v>
       </c>
-      <c r="H83" s="7" t="n">
+      <c r="H83" s="8" t="n">
         <f aca="false">IF(H82&gt;$L39,(SUMPRODUCT($B46:$K46/(1+H82)^$B$16:$K$16)+$L46/(H82-$L39)/(1+H82)^$K$16+$B$7+$B$8)/$B$6,"n/a")</f>
         <v>79.4628213320494</v>
       </c>
-      <c r="I83" s="7" t="n">
+      <c r="I83" s="8" t="n">
         <f aca="false">IF(I82&gt;$L39,(SUMPRODUCT($B46:$K46/(1+I82)^$B$16:$K$16)+$L46/(I82-$L39)/(1+I82)^$K$16+$B$7+$B$8)/$B$6,"n/a")</f>
         <v>68.4362980512501</v>
       </c>
-      <c r="J83" s="7" t="n">
+      <c r="J83" s="8" t="n">
         <f aca="false">IF(J82&gt;$L39,(SUMPRODUCT($B46:$K46/(1+J82)^$B$16:$K$16)+$L46/(J82-$L39)/(1+J82)^$K$16+$B$7+$B$8)/$B$6,"n/a")</f>
         <v>59.9023231172952</v>
       </c>
-      <c r="K83" s="7" t="n">
+      <c r="K83" s="8" t="n">
         <f aca="false">IF(K82&gt;$L39,(SUMPRODUCT($B46:$K46/(1+K82)^$B$16:$K$16)+$L46/(K82-$L39)/(1+K82)^$K$16+$B$7+$B$8)/$B$6,"n/a")</f>
         <v>53.1107571264277</v>
       </c>
     </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="0" t="s">
-        <v>91</v>
-      </c>
-      <c r="B84" s="6" t="n">
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A84" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B84" s="7" t="n">
         <f aca="false">IFERROR(B83/$B$4-1,"n/a")</f>
         <v>2.94231442913588</v>
       </c>
-      <c r="C84" s="6" t="n">
+      <c r="C84" s="7" t="n">
         <f aca="false">IFERROR(C83/$B$4-1,"n/a")</f>
         <v>0.934017439434276</v>
       </c>
-      <c r="D84" s="6" t="n">
+      <c r="D84" s="7" t="n">
         <f aca="false">IFERROR(D83/$B$4-1,"n/a")</f>
         <v>0.265797130750646</v>
       </c>
-      <c r="E84" s="6" t="n">
+      <c r="E84" s="7" t="n">
         <f aca="false">IFERROR(E83/$B$4-1,"n/a")</f>
         <v>-0.0674655123090162</v>
       </c>
-      <c r="F84" s="6" t="n">
+      <c r="F84" s="7" t="n">
         <f aca="false">IFERROR(F83/$B$4-1,"n/a")</f>
         <v>-0.266790352132973</v>
       </c>
-      <c r="G84" s="6" t="n">
+      <c r="G84" s="7" t="n">
         <f aca="false">IFERROR(G83/$B$4-1,"n/a")</f>
         <v>-0.399181025492253</v>
       </c>
-      <c r="H84" s="6" t="n">
+      <c r="H84" s="7" t="n">
         <f aca="false">IFERROR(H83/$B$4-1,"n/a")</f>
         <v>-0.493351049910422</v>
       </c>
-      <c r="I84" s="6" t="n">
+      <c r="I84" s="7" t="n">
         <f aca="false">IFERROR(I83/$B$4-1,"n/a")</f>
         <v>-0.563655329946123</v>
       </c>
-      <c r="J84" s="6" t="n">
+      <c r="J84" s="7" t="n">
         <f aca="false">IFERROR(J83/$B$4-1,"n/a")</f>
         <v>-0.618067309887177</v>
       </c>
-      <c r="K84" s="6" t="n">
+      <c r="K84" s="7" t="n">
         <f aca="false">IFERROR(K83/$B$4-1,"n/a")</f>
         <v>-0.661369821943205</v>
       </c>
     </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="8" t="s">
-        <v>92</v>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A86" s="9" t="s">
+        <v>84</v>
       </c>
       <c r="B86" s="26" t="n">
         <f aca="false">IFERROR(IF(MATCH($B$4,$B$83:$K$83,-1)=10,"above 14%",INDEX($B$82:$K$82,MATCH($B$4,$B$83:$K$83,-1))+(INDEX($B$83:$K$83,MATCH($B$4,$B$83:$K$83,-1))-$B$4)/(INDEX($B$83:$K$83,MATCH($B$4,$B$83:$K$83,-1))-INDEX($B$83:$K$83,MATCH($B$4,$B$83:$K$83,-1)+1))*(INDEX($B$82:$K$82,MATCH($B$4,$B$83:$K$83,-1)+1)-INDEX($B$82:$K$82,MATCH($B$4,$B$83:$K$83,-1)))),"below 5%")</f>
         <v>0.0779756053156868</v>
       </c>
-      <c r="C86" s="2" t="s">
-        <v>93</v>
+      <c r="C86" s="3" t="s">
+        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -3358,275 +3305,275 @@
   <dimension ref="A1:C29"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="50"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="50"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="46"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B5" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B6" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B7" s="14" t="n">
+        <v>0.0531</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="B8" s="14" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="B9" s="14" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="B5" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="C5" s="2" t="s">
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="18" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="B12" s="18" t="s">
         <v>98</v>
       </c>
-      <c r="B6" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="C6" s="2" t="s">
+      <c r="C12" s="18" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="s">
         <v>100</v>
-      </c>
-      <c r="B7" s="13" t="n">
-        <v>0.0531</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
-        <v>102</v>
-      </c>
-      <c r="B8" s="13" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
-        <v>103</v>
-      </c>
-      <c r="B9" s="13" t="n">
-        <v>0.012</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="18" t="s">
-        <v>105</v>
-      </c>
-      <c r="B12" s="18" t="s">
-        <v>106</v>
-      </c>
-      <c r="C12" s="18" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
-        <v>108</v>
       </c>
       <c r="B13" s="27" t="n">
         <v>0.99</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
-        <v>109</v>
+      <c r="C13" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="s">
+        <v>101</v>
       </c>
       <c r="B14" s="28"/>
-      <c r="C14" s="2" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
-        <v>111</v>
+      <c r="C14" s="3" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
+        <v>103</v>
       </c>
       <c r="B15" s="28" t="n">
         <f aca="false">0.67*IF(ISNUMBER(B14),B14,B13)+0.33</f>
         <v>0.9933</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
-        <v>113</v>
+      <c r="C15" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
+        <v>105</v>
       </c>
       <c r="B16" s="28" t="n">
         <f aca="false">IF($B$6=1,IF(ISNUMBER(B14),B14,B13),B15)</f>
         <v>0.9933</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
-        <v>115</v>
+      <c r="C16" s="3" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
+        <v>107</v>
       </c>
       <c r="B17" s="25" t="n">
         <f aca="false">$B$7+B16*$B$8</f>
         <v>0.102765</v>
       </c>
-      <c r="C17" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
-        <v>117</v>
+      <c r="C17" s="3" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="s">
+        <v>109</v>
       </c>
       <c r="B18" s="25" t="n">
         <f aca="false">$B$7+$B$9</f>
         <v>0.0651</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
-        <v>40</v>
-      </c>
-      <c r="B19" s="5" t="n">
+      <c r="C18" s="3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B19" s="6" t="n">
         <f aca="false">NOW!B9</f>
         <v>0.2</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
-        <v>120</v>
+      <c r="C19" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="s">
+        <v>112</v>
       </c>
       <c r="B20" s="25" t="n">
         <f aca="false">B18*(1-B19)</f>
         <v>0.05208</v>
       </c>
-      <c r="C20" s="2"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
-        <v>121</v>
+      <c r="C20" s="3"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="s">
+        <v>113</v>
       </c>
       <c r="B21" s="29" t="n">
         <f aca="false">NOW!B4*NOW!B6</f>
         <v>161.5452</v>
       </c>
-      <c r="C21" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
-        <v>123</v>
+      <c r="C21" s="3" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="s">
+        <v>115</v>
       </c>
       <c r="B22" s="30" t="n">
         <v>8.45</v>
       </c>
-      <c r="C22" s="2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
-        <v>125</v>
+      <c r="C22" s="3" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="s">
+        <v>117</v>
       </c>
       <c r="B23" s="25" t="n">
         <f aca="false">B21/(B21+B22)</f>
         <v>0.950292714147223</v>
       </c>
-      <c r="C23" s="2"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
-        <v>126</v>
+      <c r="C23" s="3"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="s">
+        <v>118</v>
       </c>
       <c r="B24" s="25" t="n">
         <f aca="false">B22/(B21+B22)</f>
         <v>0.049707285852777</v>
       </c>
-      <c r="C24" s="2"/>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
-        <v>127</v>
+      <c r="C24" s="3"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1" t="s">
+        <v>119</v>
       </c>
       <c r="B25" s="25" t="n">
         <f aca="false">B23*B17+B24*B20</f>
         <v>0.100245586216552</v>
       </c>
-      <c r="C25" s="2" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
-        <v>129</v>
+      <c r="C25" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1" t="s">
+        <v>121</v>
       </c>
       <c r="B26" s="31" t="n">
         <v>0.095</v>
       </c>
-      <c r="C26" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="0" t="s">
-        <v>131</v>
+      <c r="C26" s="3" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="1" t="s">
+        <v>123</v>
       </c>
       <c r="B27" s="26" t="n">
         <f aca="false">IF($B$5=1,B25,B26)</f>
         <v>0.095</v>
       </c>
-      <c r="C27" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="0" t="s">
-        <v>133</v>
-      </c>
-      <c r="B28" s="0" t="str">
+      <c r="C27" s="3" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B28" s="1" t="str">
         <f aca="false">IF(B27&gt;MAX(NOW!L21,NOW!L39,NOW!L57),"OK","WACC must exceed growth")</f>
         <v>OK</v>
       </c>
-      <c r="C28" s="2"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="0" t="s">
-        <v>134</v>
+      <c r="C28" s="3"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1" t="s">
+        <v>126</v>
       </c>
       <c r="B29" s="25" t="n">
         <f aca="false">B27</f>
         <v>0.095</v>
       </c>
-      <c r="C29" s="2" t="s">
-        <v>135</v>
+      <c r="C29" s="3" t="s">
+        <v>127</v>
       </c>
     </row>
   </sheetData>

--- a/models/holdings/NOW_Valuation.xlsx
+++ b/models/holdings/NOW_Valuation.xlsx
@@ -303,7 +303,7 @@
     <t xml:space="preserve">Risk-free rate (10-year Treasury)</t>
   </si>
   <si>
-    <t xml:space="preserve">FRED via MacroRadar, Oct 6, 2026 (same as earlier journal models)</t>
+    <t xml:space="preserve">10-year Treasury yield at the close on 2026-10-28; assumed rates below move with it</t>
   </si>
   <si>
     <t xml:space="preserve">Equity risk premium</t>
@@ -989,23 +989,23 @@
       </c>
       <c r="D5" s="6" t="n">
         <f aca="false">NOW!B10</f>
-        <v>0.095</v>
+        <v>0.0922</v>
       </c>
       <c r="E5" s="5" t="n">
         <f aca="false">NOW!B75</f>
-        <v>58.8528253261598</v>
+        <v>62.011421773214</v>
       </c>
       <c r="F5" s="5" t="n">
         <f aca="false">NOW!B76</f>
-        <v>103.660517846071</v>
+        <v>109.738485810207</v>
       </c>
       <c r="G5" s="5" t="n">
         <f aca="false">NOW!B77</f>
-        <v>151.933982066243</v>
+        <v>161.837329414344</v>
       </c>
       <c r="H5" s="7" t="n">
         <f aca="false">F5/C5-1</f>
-        <v>-0.339068363644023</v>
+        <v>-0.300315698736245</v>
       </c>
       <c r="I5" s="6" t="n">
         <f aca="false">NOW!B86</f>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="J5" s="8" t="n">
         <f aca="false">IF(F5&lt;10,ROUND(F5*4,0)/4,IF(F5&lt;100,ROUND(F5,0),ROUND(F5/5,0)*5))</f>
-        <v>105</v>
+        <v>110</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1172,7 +1172,7 @@
       </c>
       <c r="B10" s="15" t="n">
         <f aca="false">WACC!B29</f>
-        <v>0.095</v>
+        <v>0.0922</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>35</v>
@@ -1773,43 +1773,43 @@
       </c>
       <c r="B29" s="23" t="n">
         <f aca="false">1/(1+$B$10)^B$16</f>
-        <v>0.955636965134993</v>
+        <v>0.956861132304626</v>
       </c>
       <c r="C29" s="23" t="n">
         <f aca="false">1/(1+$B$10)^C$16</f>
-        <v>0.87272782204109</v>
+        <v>0.876086002842543</v>
       </c>
       <c r="D29" s="23" t="n">
         <f aca="false">1/(1+$B$10)^D$16</f>
-        <v>0.797011709626566</v>
+        <v>0.802129649187459</v>
       </c>
       <c r="E29" s="23" t="n">
         <f aca="false">1/(1+$B$10)^E$16</f>
-        <v>0.72786457500143</v>
+        <v>0.734416452286632</v>
       </c>
       <c r="F29" s="23" t="n">
         <f aca="false">1/(1+$B$10)^F$16</f>
-        <v>0.664716506850621</v>
+        <v>0.672419384990507</v>
       </c>
       <c r="G29" s="23" t="n">
         <f aca="false">1/(1+$B$10)^G$16</f>
-        <v>0.607047038219745</v>
+        <v>0.615655910081036</v>
       </c>
       <c r="H29" s="23" t="n">
         <f aca="false">1/(1+$B$10)^H$16</f>
-        <v>0.554380856821685</v>
+        <v>0.563684224575202</v>
       </c>
       <c r="I29" s="23" t="n">
         <f aca="false">1/(1+$B$10)^I$16</f>
-        <v>0.506283887508388</v>
+        <v>0.516099821072333</v>
       </c>
       <c r="J29" s="23" t="n">
         <f aca="false">1/(1+$B$10)^J$16</f>
-        <v>0.462359714619533</v>
+        <v>0.47253233938137</v>
       </c>
       <c r="K29" s="23" t="n">
         <f aca="false">1/(1+$B$10)^K$16</f>
-        <v>0.422246314721034</v>
+        <v>0.432642683923613</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1818,43 +1818,43 @@
       </c>
       <c r="B30" s="20" t="n">
         <f aca="false">B28*B29</f>
-        <v>1.9531308293429</v>
+        <v>1.95563278220419</v>
       </c>
       <c r="C30" s="20" t="n">
         <f aca="false">C28*C29</f>
-        <v>2.1069395079716</v>
+        <v>2.11504682806247</v>
       </c>
       <c r="D30" s="20" t="n">
         <f aca="false">D28*D29</f>
-        <v>2.23434262676712</v>
+        <v>2.24869025853212</v>
       </c>
       <c r="E30" s="20" t="n">
         <f aca="false">E28*E29</f>
-        <v>2.33644528575459</v>
+        <v>2.35747681184009</v>
       </c>
       <c r="F30" s="20" t="n">
         <f aca="false">F28*F29</f>
-        <v>2.41398446627872</v>
+        <v>2.44195823853153</v>
       </c>
       <c r="G30" s="20" t="n">
         <f aca="false">G28*G29</f>
-        <v>2.42597867163303</v>
+        <v>2.4603828251951</v>
       </c>
       <c r="H30" s="20" t="n">
         <f aca="false">H28*H29</f>
-        <v>2.41883312440548</v>
+        <v>2.45942488332686</v>
       </c>
       <c r="I30" s="20" t="n">
         <f aca="false">I28*I29</f>
-        <v>2.39278167837633</v>
+        <v>2.4391734095127</v>
       </c>
       <c r="J30" s="20" t="n">
         <f aca="false">J28*J29</f>
-        <v>2.34848097236068</v>
+        <v>2.40015116536571</v>
       </c>
       <c r="K30" s="20" t="n">
         <f aca="false">K28*K29</f>
-        <v>2.28698591359201</v>
+        <v>2.34329510822526</v>
       </c>
       <c r="L30" s="20"/>
     </row>
@@ -1864,7 +1864,7 @@
       </c>
       <c r="B31" s="20" t="n">
         <f aca="false">L28/($B$10-L21)</f>
-        <v>93.4300801074509</v>
+        <v>98.0035805322911</v>
       </c>
       <c r="C31" s="1" t="str">
         <f aca="false">IF($B$10&gt;L21,"","Discount rate must exceed terminal growth")</f>
@@ -1877,7 +1877,7 @@
       </c>
       <c r="B32" s="20" t="n">
         <f aca="false">B31/(1+$B$10)^$K$16</f>
-        <v>39.4505070094622</v>
+        <v>42.4005321156144</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="B33" s="20" t="n">
         <f aca="false">SUM(B30:K30)+B32+$B$7+$B$8</f>
-        <v>60.6184100859446</v>
+        <v>63.8717644264104</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1895,7 +1895,7 @@
       </c>
       <c r="B34" s="24" t="n">
         <f aca="false">B33/$B$6</f>
-        <v>58.8528253261598</v>
+        <v>62.011421773214</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="B35" s="7" t="n">
         <f aca="false">B34/$B$4-1</f>
-        <v>-0.624758828575875</v>
+        <v>-0.604619856074891</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2352,43 +2352,43 @@
       </c>
       <c r="B47" s="23" t="n">
         <f aca="false">1/(1+$B$10)^B$16</f>
-        <v>0.955636965134993</v>
+        <v>0.956861132304626</v>
       </c>
       <c r="C47" s="23" t="n">
         <f aca="false">1/(1+$B$10)^C$16</f>
-        <v>0.87272782204109</v>
+        <v>0.876086002842543</v>
       </c>
       <c r="D47" s="23" t="n">
         <f aca="false">1/(1+$B$10)^D$16</f>
-        <v>0.797011709626566</v>
+        <v>0.802129649187459</v>
       </c>
       <c r="E47" s="23" t="n">
         <f aca="false">1/(1+$B$10)^E$16</f>
-        <v>0.72786457500143</v>
+        <v>0.734416452286632</v>
       </c>
       <c r="F47" s="23" t="n">
         <f aca="false">1/(1+$B$10)^F$16</f>
-        <v>0.664716506850621</v>
+        <v>0.672419384990507</v>
       </c>
       <c r="G47" s="23" t="n">
         <f aca="false">1/(1+$B$10)^G$16</f>
-        <v>0.607047038219745</v>
+        <v>0.615655910081036</v>
       </c>
       <c r="H47" s="23" t="n">
         <f aca="false">1/(1+$B$10)^H$16</f>
-        <v>0.554380856821685</v>
+        <v>0.563684224575202</v>
       </c>
       <c r="I47" s="23" t="n">
         <f aca="false">1/(1+$B$10)^I$16</f>
-        <v>0.506283887508388</v>
+        <v>0.516099821072333</v>
       </c>
       <c r="J47" s="23" t="n">
         <f aca="false">1/(1+$B$10)^J$16</f>
-        <v>0.462359714619533</v>
+        <v>0.47253233938137</v>
       </c>
       <c r="K47" s="23" t="n">
         <f aca="false">1/(1+$B$10)^K$16</f>
-        <v>0.422246314721034</v>
+        <v>0.432642683923613</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2397,43 +2397,43 @@
       </c>
       <c r="B48" s="20" t="n">
         <f aca="false">B46*B47</f>
-        <v>2.38087393493732</v>
+        <v>2.38392382502374</v>
       </c>
       <c r="C48" s="20" t="n">
         <f aca="false">C46*C47</f>
-        <v>2.83741269501999</v>
+        <v>2.84833081244168</v>
       </c>
       <c r="D48" s="20" t="n">
         <f aca="false">D46*D47</f>
-        <v>3.30217891532479</v>
+        <v>3.32338356251348</v>
       </c>
       <c r="E48" s="20" t="n">
         <f aca="false">E46*E47</f>
-        <v>3.65184214569718</v>
+        <v>3.68471422441249</v>
       </c>
       <c r="F48" s="20" t="n">
         <f aca="false">F46*F47</f>
-        <v>3.97021875211739</v>
+        <v>4.0162265026713</v>
       </c>
       <c r="G48" s="20" t="n">
         <f aca="false">G46*G47</f>
-        <v>4.05741975724965</v>
+        <v>4.11496028471861</v>
       </c>
       <c r="H48" s="20" t="n">
         <f aca="false">H46*H47</f>
-        <v>4.08754366805858</v>
+        <v>4.15613896943772</v>
       </c>
       <c r="I48" s="20" t="n">
         <f aca="false">I46*I47</f>
-        <v>4.05853575793596</v>
+        <v>4.13722346329204</v>
       </c>
       <c r="J48" s="20" t="n">
         <f aca="false">J46*J47</f>
-        <v>3.97086974929243</v>
+        <v>4.05823499038166</v>
       </c>
       <c r="K48" s="20" t="n">
         <f aca="false">K46*K47</f>
-        <v>3.82756994549782</v>
+        <v>3.92181074503773</v>
       </c>
       <c r="L48" s="20"/>
     </row>
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B49" s="20" t="n">
         <f aca="false">L46/($B$10-L39)</f>
-        <v>171.406748944959</v>
+        <v>180.600980689133</v>
       </c>
       <c r="C49" s="1" t="str">
         <f aca="false">IF($B$10&gt;L39,"","Discount rate must exceed terminal growth")</f>
@@ -2456,7 +2456,7 @@
       </c>
       <c r="B50" s="20" t="n">
         <f aca="false">B49/(1+$B$10)^$K$16</f>
-        <v>72.3758680603224</v>
+        <v>78.1356930045831</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2465,7 +2465,7 @@
       </c>
       <c r="B51" s="20" t="n">
         <f aca="false">SUM(B48:K48)+B50+$B$7+$B$8</f>
-        <v>106.770333381454</v>
+        <v>113.030640384514</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="B52" s="24" t="n">
         <f aca="false">B51/$B$6</f>
-        <v>103.660517846071</v>
+        <v>109.738485810207</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="B53" s="7" t="n">
         <f aca="false">B52/$B$4-1</f>
-        <v>-0.339068363644023</v>
+        <v>-0.300315698736245</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2931,43 +2931,43 @@
       </c>
       <c r="B65" s="23" t="n">
         <f aca="false">1/(1+$B$10)^B$16</f>
-        <v>0.955636965134993</v>
+        <v>0.956861132304626</v>
       </c>
       <c r="C65" s="23" t="n">
         <f aca="false">1/(1+$B$10)^C$16</f>
-        <v>0.87272782204109</v>
+        <v>0.876086002842543</v>
       </c>
       <c r="D65" s="23" t="n">
         <f aca="false">1/(1+$B$10)^D$16</f>
-        <v>0.797011709626566</v>
+        <v>0.802129649187459</v>
       </c>
       <c r="E65" s="23" t="n">
         <f aca="false">1/(1+$B$10)^E$16</f>
-        <v>0.72786457500143</v>
+        <v>0.734416452286632</v>
       </c>
       <c r="F65" s="23" t="n">
         <f aca="false">1/(1+$B$10)^F$16</f>
-        <v>0.664716506850621</v>
+        <v>0.672419384990507</v>
       </c>
       <c r="G65" s="23" t="n">
         <f aca="false">1/(1+$B$10)^G$16</f>
-        <v>0.607047038219745</v>
+        <v>0.615655910081036</v>
       </c>
       <c r="H65" s="23" t="n">
         <f aca="false">1/(1+$B$10)^H$16</f>
-        <v>0.554380856821685</v>
+        <v>0.563684224575202</v>
       </c>
       <c r="I65" s="23" t="n">
         <f aca="false">1/(1+$B$10)^I$16</f>
-        <v>0.506283887508388</v>
+        <v>0.516099821072333</v>
       </c>
       <c r="J65" s="23" t="n">
         <f aca="false">1/(1+$B$10)^J$16</f>
-        <v>0.462359714619533</v>
+        <v>0.47253233938137</v>
       </c>
       <c r="K65" s="23" t="n">
         <f aca="false">1/(1+$B$10)^K$16</f>
-        <v>0.422246314721034</v>
+        <v>0.432642683923613</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2976,43 +2976,43 @@
       </c>
       <c r="B66" s="20" t="n">
         <f aca="false">B64*B65</f>
-        <v>2.59646563427178</v>
+        <v>2.59979169647167</v>
       </c>
       <c r="C66" s="20" t="n">
         <f aca="false">C64*C65</f>
-        <v>3.34638756083435</v>
+        <v>3.35926416929945</v>
       </c>
       <c r="D66" s="20" t="n">
         <f aca="false">D64*D65</f>
-        <v>3.9691183139403</v>
+        <v>3.99460565295355</v>
       </c>
       <c r="E66" s="20" t="n">
         <f aca="false">E64*E65</f>
-        <v>4.59806609319904</v>
+        <v>4.63945561238511</v>
       </c>
       <c r="F66" s="20" t="n">
         <f aca="false">F64*F65</f>
-        <v>5.01156363174957</v>
+        <v>5.06963871119743</v>
       </c>
       <c r="G66" s="20" t="n">
         <f aca="false">G64*G65</f>
-        <v>5.27978767664752</v>
+        <v>5.35466328381031</v>
       </c>
       <c r="H66" s="20" t="n">
         <f aca="false">H64*H65</f>
-        <v>5.45573843025555</v>
+        <v>5.54729415473466</v>
       </c>
       <c r="I66" s="20" t="n">
         <f aca="false">I64*I65</f>
-        <v>5.52761095138074</v>
+        <v>5.63478138126171</v>
       </c>
       <c r="J66" s="20" t="n">
         <f aca="false">J64*J65</f>
-        <v>5.48926649909737</v>
+        <v>5.6100388037498</v>
       </c>
       <c r="K66" s="20" t="n">
         <f aca="false">K64*K65</f>
-        <v>5.34100441720796</v>
+        <v>5.47250835672862</v>
       </c>
       <c r="L66" s="20"/>
     </row>
@@ -3022,7 +3022,7 @@
       </c>
       <c r="B67" s="20" t="n">
         <f aca="false">L64/($B$10-L57)</f>
-        <v>264.364633693476</v>
+        <v>280.047281454953</v>
       </c>
       <c r="C67" s="1" t="str">
         <f aca="false">IF($B$10&gt;L57,"","Discount rate must exceed terminal growth")</f>
@@ -3035,7 +3035,7 @@
       </c>
       <c r="B68" s="20" t="n">
         <f aca="false">B67/(1+$B$10)^$K$16</f>
-        <v>111.626992319646</v>
+        <v>121.160407474182</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3044,7 +3044,7 @@
       </c>
       <c r="B69" s="20" t="n">
         <f aca="false">SUM(B66:K66)+B68+$B$7+$B$8</f>
-        <v>156.492001528231</v>
+        <v>166.692449296775</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B70" s="24" t="n">
         <f aca="false">B69/$B$6</f>
-        <v>151.933982066243</v>
+        <v>161.837329414344</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3062,7 +3062,7 @@
       </c>
       <c r="B71" s="7" t="n">
         <f aca="false">B70/$B$4-1</f>
-        <v>-0.0312803999856973</v>
+        <v>0.031862595092734</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3089,11 +3089,11 @@
       </c>
       <c r="B75" s="8" t="n">
         <f aca="false">B34</f>
-        <v>58.8528253261598</v>
+        <v>62.011421773214</v>
       </c>
       <c r="C75" s="7" t="n">
         <f aca="false">B75/$B$4-1</f>
-        <v>-0.624758828575875</v>
+        <v>-0.604619856074891</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3102,11 +3102,11 @@
       </c>
       <c r="B76" s="8" t="n">
         <f aca="false">B52</f>
-        <v>103.660517846071</v>
+        <v>109.738485810207</v>
       </c>
       <c r="C76" s="7" t="n">
         <f aca="false">B76/$B$4-1</f>
-        <v>-0.339068363644023</v>
+        <v>-0.300315698736245</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3115,11 +3115,11 @@
       </c>
       <c r="B77" s="8" t="n">
         <f aca="false">B70</f>
-        <v>151.933982066243</v>
+        <v>161.837329414344</v>
       </c>
       <c r="C77" s="7" t="n">
         <f aca="false">B77/$B$4-1</f>
-        <v>-0.0312803999856973</v>
+        <v>0.031862595092734</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3128,11 +3128,11 @@
       </c>
       <c r="B78" s="8" t="n">
         <f aca="false">INDEX(B34:B70,1+($B$13-1)*18)</f>
-        <v>103.660517846071</v>
+        <v>109.738485810207</v>
       </c>
       <c r="C78" s="7" t="n">
         <f aca="false">B78/$B$4-1</f>
-        <v>-0.339068363644023</v>
+        <v>-0.300315698736245</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3141,7 +3141,7 @@
       </c>
       <c r="B79" s="25" t="n">
         <f aca="false">B50/(SUM(B48:K48)+B50)</f>
-        <v>0.666933705464378</v>
+        <v>0.680739301879042</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3347,7 +3347,7 @@
         <v>92</v>
       </c>
       <c r="B7" s="14" t="n">
-        <v>0.0531</v>
+        <v>0.0503</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>93</v>
@@ -3436,7 +3436,7 @@
       </c>
       <c r="B17" s="25" t="n">
         <f aca="false">$B$7+B16*$B$8</f>
-        <v>0.102765</v>
+        <v>0.099965</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>108</v>
@@ -3448,7 +3448,7 @@
       </c>
       <c r="B18" s="25" t="n">
         <f aca="false">$B$7+$B$9</f>
-        <v>0.0651</v>
+        <v>0.0623</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>110</v>
@@ -3472,7 +3472,7 @@
       </c>
       <c r="B20" s="25" t="n">
         <f aca="false">B18*(1-B19)</f>
-        <v>0.05208</v>
+        <v>0.04984</v>
       </c>
       <c r="C20" s="3"/>
     </row>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="B25" s="25" t="n">
         <f aca="false">B23*B17+B24*B20</f>
-        <v>0.100245586216552</v>
+        <v>0.0974734222966296</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>120</v>
@@ -3536,7 +3536,7 @@
         <v>121</v>
       </c>
       <c r="B26" s="31" t="n">
-        <v>0.095</v>
+        <v>0.0922</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>122</v>
@@ -3548,7 +3548,7 @@
       </c>
       <c r="B27" s="26" t="n">
         <f aca="false">IF($B$5=1,B25,B26)</f>
-        <v>0.095</v>
+        <v>0.0922</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>124</v>
@@ -3570,7 +3570,7 @@
       </c>
       <c r="B29" s="25" t="n">
         <f aca="false">B27</f>
-        <v>0.095</v>
+        <v>0.0922</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>127</v>

--- a/models/holdings/NOW_Valuation.xlsx
+++ b/models/holdings/NOW_Valuation.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="127">
   <si>
     <t xml:space="preserve">ServiceNow (NOW): valuation summary</t>
   </si>
@@ -90,15 +90,12 @@
     <t xml:space="preserve">Share price ($)</t>
   </si>
   <si>
-    <t xml:space="preserve">Oct 23, 2026 intraday (Yahoo Finance via the site's price feed)</t>
+    <t xml:space="preserve">Oct 28, 2026 close (before Q3 results)</t>
   </si>
   <si>
     <t xml:space="preserve">Price date</t>
   </si>
   <si>
-    <t xml:space="preserve">Oct 23, 2026</t>
-  </si>
-  <si>
     <t xml:space="preserve">Text</t>
   </si>
   <si>
@@ -117,7 +114,7 @@
     <t xml:space="preserve">Other non-operating assets, less outside claims</t>
   </si>
   <si>
-    <t xml:space="preserve">Long-term investments excluded (conservative)</t>
+    <t xml:space="preserve">Long-term investments ($2.35B) excluded (conservative)</t>
   </si>
   <si>
     <t xml:space="preserve">Tax rate</t>
@@ -141,7 +138,7 @@
     <t xml:space="preserve">Base-year revenue (2026E)</t>
   </si>
   <si>
-    <t xml:space="preserve">2026E consensus $16.22B (Stock Analysis). Margins are after stock pay (GAAP-like), not the 31.5% non-GAAP figure</t>
+    <t xml:space="preserve">2026E: subscription guide $15.785B plus about $0.55B of services (Q3 2026 release, Oct 28). Q4 cRPO guided to 18.5% growth. Margins are after stock pay (GAAP-like), not the 31.5% non-GAAP figure</t>
   </si>
   <si>
     <t xml:space="preserve">Selected scenario (1 Bear, 2 Base, 3 Bull)</t>
@@ -926,7 +923,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="32"/>
@@ -985,7 +982,7 @@
       </c>
       <c r="C5" s="5" t="n">
         <f aca="false">NOW!B4</f>
-        <v>156.84</v>
+        <v>150.13</v>
       </c>
       <c r="D5" s="6" t="n">
         <f aca="false">NOW!B10</f>
@@ -993,23 +990,23 @@
       </c>
       <c r="E5" s="5" t="n">
         <f aca="false">NOW!B75</f>
-        <v>62.011421773214</v>
+        <v>60.4012540367849</v>
       </c>
       <c r="F5" s="5" t="n">
         <f aca="false">NOW!B76</f>
-        <v>109.738485810207</v>
+        <v>107.760479429948</v>
       </c>
       <c r="G5" s="5" t="n">
         <f aca="false">NOW!B77</f>
-        <v>161.837329414344</v>
+        <v>159.457790520758</v>
       </c>
       <c r="H5" s="7" t="n">
         <f aca="false">F5/C5-1</f>
-        <v>-0.300315698736245</v>
+        <v>-0.282218880770347</v>
       </c>
       <c r="I5" s="6" t="n">
         <f aca="false">NOW!B86</f>
-        <v>0.0779756053156868</v>
+        <v>0.0788179565543007</v>
       </c>
       <c r="J5" s="8" t="n">
         <f aca="false">IF(F5&lt;10,ROUND(F5*4,0)/4,IF(F5&lt;100,ROUND(F5,0),ROUND(F5/5,0)*5))</f>
@@ -1026,7 +1023,7 @@
         <v>11</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1034,7 +1031,7 @@
         <v>15</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>150</v>
+        <v>160</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1042,7 +1039,7 @@
         <v>16</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1059,12 +1056,6 @@
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="9"/>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1105,7 +1096,7 @@
         <v>21</v>
       </c>
       <c r="B4" s="10" t="n">
-        <v>156.84</v>
+        <v>150.13</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>22</v>
@@ -1116,142 +1107,142 @@
         <v>23</v>
       </c>
       <c r="B5" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>24</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" s="12" t="n">
+        <v>1.038</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>26</v>
-      </c>
-      <c r="B6" s="12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="13" t="n">
+        <v>-2.92</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>28</v>
-      </c>
-      <c r="B7" s="13" t="n">
-        <v>-1.75</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B8" s="13" t="n">
         <v>0</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B9" s="14" t="n">
         <v>0.2</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B10" s="15" t="n">
         <f aca="false">WACC!B29</f>
         <v>0.0922</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B11" s="14" t="n">
         <v>-0.05</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="B12" s="13" t="n">
+        <v>16.33</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>38</v>
-      </c>
-      <c r="B12" s="13" t="n">
-        <v>16.22</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B13" s="16" t="n">
         <v>2</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="B15" s="17" t="s">
         <v>42</v>
       </c>
-      <c r="B15" s="17" t="s">
+      <c r="C15" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="C15" s="17" t="s">
+      <c r="D15" s="17" t="s">
         <v>44</v>
       </c>
-      <c r="D15" s="17" t="s">
+      <c r="E15" s="17" t="s">
         <v>45</v>
       </c>
-      <c r="E15" s="17" t="s">
+      <c r="F15" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="F15" s="17" t="s">
+      <c r="G15" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="G15" s="17" t="s">
+      <c r="H15" s="17" t="s">
         <v>48</v>
       </c>
-      <c r="H15" s="17" t="s">
+      <c r="I15" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="I15" s="17" t="s">
+      <c r="J15" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="J15" s="17" t="s">
+      <c r="K15" s="17" t="s">
         <v>51</v>
       </c>
-      <c r="K15" s="17" t="s">
+      <c r="L15" s="9" t="s">
         <v>52</v>
-      </c>
-      <c r="L15" s="9" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B16" s="11" t="n">
         <v>0.5</v>
@@ -1295,7 +1286,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B17" s="1" t="n">
         <v>0</v>
@@ -1330,7 +1321,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="18" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B19" s="19"/>
       <c r="C19" s="19"/>
@@ -1346,7 +1337,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B20" s="13" t="n">
         <v>18.3</v>
@@ -1390,11 +1381,11 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B21" s="7" t="n">
         <f aca="false">B20/$B$12-1</f>
-        <v>0.128236744759556</v>
+        <v>0.120636864666259</v>
       </c>
       <c r="C21" s="7" t="n">
         <f aca="false">C20/B20-1</f>
@@ -1438,7 +1429,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B22" s="22" t="n">
         <v>0.17</v>
@@ -1481,7 +1472,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B23" s="20" t="n">
         <f aca="false">B20*B22</f>
@@ -1530,7 +1521,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B24" s="20" t="n">
         <f aca="false">B23*(1-$B$9)</f>
@@ -1579,7 +1570,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B25" s="22" t="n">
         <v>0.03</v>
@@ -1622,7 +1613,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B26" s="20" t="n">
         <f aca="false">B20*B25</f>
@@ -1671,11 +1662,11 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B27" s="20" t="n">
         <f aca="false">$B$11*(B20-$B$12)</f>
-        <v>-0.104</v>
+        <v>-0.0985000000000001</v>
       </c>
       <c r="C27" s="20" t="n">
         <f aca="false">$B$11*(C20-B20)</f>
@@ -1720,11 +1711,11 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B28" s="20" t="n">
         <f aca="false">B24-B26-B27</f>
-        <v>2.0438</v>
+        <v>2.0383</v>
       </c>
       <c r="C28" s="20" t="n">
         <f aca="false">C24-C26-C27</f>
@@ -1769,7 +1760,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B29" s="23" t="n">
         <f aca="false">1/(1+$B$10)^B$16</f>
@@ -1814,11 +1805,11 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B30" s="20" t="n">
         <f aca="false">B28*B29</f>
-        <v>1.95563278220419</v>
+        <v>1.95037004597652</v>
       </c>
       <c r="C30" s="20" t="n">
         <f aca="false">C28*C29</f>
@@ -1860,7 +1851,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B31" s="20" t="n">
         <f aca="false">L28/($B$10-L21)</f>
@@ -1873,7 +1864,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B32" s="20" t="n">
         <f aca="false">B31/(1+$B$10)^$K$16</f>
@@ -1882,34 +1873,34 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B33" s="20" t="n">
         <f aca="false">SUM(B30:K30)+B32+$B$7+$B$8</f>
-        <v>63.8717644264104</v>
+        <v>62.6965016901828</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B34" s="24" t="n">
         <f aca="false">B33/$B$6</f>
-        <v>62.011421773214</v>
+        <v>60.4012540367849</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B35" s="7" t="n">
         <f aca="false">B34/$B$4-1</f>
-        <v>-0.604619856074891</v>
+        <v>-0.597673655919637</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="18" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B37" s="19"/>
       <c r="C37" s="19"/>
@@ -1925,7 +1916,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B38" s="13" t="n">
         <v>19.2</v>
@@ -1969,11 +1960,11 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B39" s="7" t="n">
         <f aca="false">B38/$B$12-1</f>
-        <v>0.183723797780518</v>
+        <v>0.175750153092468</v>
       </c>
       <c r="C39" s="7" t="n">
         <f aca="false">C38/B38-1</f>
@@ -2017,7 +2008,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B40" s="22" t="n">
         <v>0.19</v>
@@ -2060,7 +2051,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B41" s="20" t="n">
         <f aca="false">B38*B40</f>
@@ -2109,7 +2100,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B42" s="20" t="n">
         <f aca="false">B41*(1-$B$9)</f>
@@ -2158,7 +2149,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B43" s="22" t="n">
         <v>0.03</v>
@@ -2201,7 +2192,7 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B44" s="20" t="n">
         <f aca="false">B38*B43</f>
@@ -2250,11 +2241,11 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B45" s="20" t="n">
         <f aca="false">$B$11*(B38-$B$12)</f>
-        <v>-0.149</v>
+        <v>-0.1435</v>
       </c>
       <c r="C45" s="20" t="n">
         <f aca="false">$B$11*(C38-B38)</f>
@@ -2299,11 +2290,11 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B46" s="20" t="n">
         <f aca="false">B42-B44-B45</f>
-        <v>2.4914</v>
+        <v>2.4859</v>
       </c>
       <c r="C46" s="20" t="n">
         <f aca="false">C42-C44-C45</f>
@@ -2348,7 +2339,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B47" s="23" t="n">
         <f aca="false">1/(1+$B$10)^B$16</f>
@@ -2393,11 +2384,11 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B48" s="20" t="n">
         <f aca="false">B46*B47</f>
-        <v>2.38392382502374</v>
+        <v>2.37866108879607</v>
       </c>
       <c r="C48" s="20" t="n">
         <f aca="false">C46*C47</f>
@@ -2439,7 +2430,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B49" s="20" t="n">
         <f aca="false">L46/($B$10-L39)</f>
@@ -2452,7 +2443,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B50" s="20" t="n">
         <f aca="false">B49/(1+$B$10)^$K$16</f>
@@ -2461,34 +2452,34 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B51" s="20" t="n">
         <f aca="false">SUM(B48:K48)+B50+$B$7+$B$8</f>
-        <v>113.030640384514</v>
+        <v>111.855377648286</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B52" s="24" t="n">
         <f aca="false">B51/$B$6</f>
-        <v>109.738485810207</v>
+        <v>107.760479429948</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B53" s="7" t="n">
         <f aca="false">B52/$B$4-1</f>
-        <v>-0.300315698736245</v>
+        <v>-0.282218880770347</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="18" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B55" s="19"/>
       <c r="C55" s="19"/>
@@ -2504,7 +2495,7 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B56" s="13" t="n">
         <v>19.6</v>
@@ -2548,11 +2539,11 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B57" s="7" t="n">
         <f aca="false">B56/$B$12-1</f>
-        <v>0.208384710234279</v>
+        <v>0.200244947948561</v>
       </c>
       <c r="C57" s="7" t="n">
         <f aca="false">C56/B56-1</f>
@@ -2596,7 +2587,7 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B58" s="22" t="n">
         <v>0.2</v>
@@ -2639,7 +2630,7 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B59" s="20" t="n">
         <f aca="false">B56*B58</f>
@@ -2688,7 +2679,7 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B60" s="20" t="n">
         <f aca="false">B59*(1-$B$9)</f>
@@ -2737,7 +2728,7 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B61" s="22" t="n">
         <v>0.03</v>
@@ -2780,7 +2771,7 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B62" s="20" t="n">
         <f aca="false">B56*B61</f>
@@ -2829,11 +2820,11 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B63" s="20" t="n">
         <f aca="false">$B$11*(B56-$B$12)</f>
-        <v>-0.169</v>
+        <v>-0.1635</v>
       </c>
       <c r="C63" s="20" t="n">
         <f aca="false">$B$11*(C56-B56)</f>
@@ -2878,11 +2869,11 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B64" s="20" t="n">
         <f aca="false">B60-B62-B63</f>
-        <v>2.717</v>
+        <v>2.7115</v>
       </c>
       <c r="C64" s="20" t="n">
         <f aca="false">C60-C62-C63</f>
@@ -2927,7 +2918,7 @@
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B65" s="23" t="n">
         <f aca="false">1/(1+$B$10)^B$16</f>
@@ -2972,11 +2963,11 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B66" s="20" t="n">
         <f aca="false">B64*B65</f>
-        <v>2.59979169647167</v>
+        <v>2.59452896024399</v>
       </c>
       <c r="C66" s="20" t="n">
         <f aca="false">C64*C65</f>
@@ -3018,7 +3009,7 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B67" s="20" t="n">
         <f aca="false">L64/($B$10-L57)</f>
@@ -3031,7 +3022,7 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B68" s="20" t="n">
         <f aca="false">B67/(1+$B$10)^$K$16</f>
@@ -3040,38 +3031,38 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B69" s="20" t="n">
         <f aca="false">SUM(B66:K66)+B68+$B$7+$B$8</f>
-        <v>166.692449296775</v>
+        <v>165.517186560547</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B70" s="24" t="n">
         <f aca="false">B69/$B$6</f>
-        <v>161.837329414344</v>
+        <v>159.457790520758</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B71" s="7" t="n">
         <f aca="false">B70/$B$4-1</f>
-        <v>0.031862595092734</v>
+        <v>0.0621314229052037</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B74" s="19"/>
       <c r="C74" s="18" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D74" s="19"/>
       <c r="E74" s="19"/>
@@ -3085,68 +3076,68 @@
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B75" s="8" t="n">
         <f aca="false">B34</f>
-        <v>62.011421773214</v>
+        <v>60.4012540367849</v>
       </c>
       <c r="C75" s="7" t="n">
         <f aca="false">B75/$B$4-1</f>
-        <v>-0.604619856074891</v>
+        <v>-0.597673655919637</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B76" s="8" t="n">
         <f aca="false">B52</f>
-        <v>109.738485810207</v>
+        <v>107.760479429948</v>
       </c>
       <c r="C76" s="7" t="n">
         <f aca="false">B76/$B$4-1</f>
-        <v>-0.300315698736245</v>
+        <v>-0.282218880770347</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B77" s="8" t="n">
         <f aca="false">B70</f>
-        <v>161.837329414344</v>
+        <v>159.457790520758</v>
       </c>
       <c r="C77" s="7" t="n">
         <f aca="false">B77/$B$4-1</f>
-        <v>0.031862595092734</v>
+        <v>0.0621314229052037</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B78" s="8" t="n">
         <f aca="false">INDEX(B34:B70,1+($B$13-1)*18)</f>
-        <v>109.738485810207</v>
+        <v>107.760479429948</v>
       </c>
       <c r="C78" s="7" t="n">
         <f aca="false">B78/$B$4-1</f>
-        <v>-0.300315698736245</v>
+        <v>-0.282218880770347</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B79" s="25" t="n">
         <f aca="false">B50/(SUM(B48:K48)+B50)</f>
-        <v>0.680739301879042</v>
+        <v>0.680770515467348</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3186,104 +3177,104 @@
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B83" s="8" t="n">
         <f aca="false">IF(B82&gt;$L39,(SUMPRODUCT($B46:$K46/(1+B82)^$B$16:$K$16)+$L46/(B82-$L39)/(1+B82)^$K$16+$B$7+$B$8)/$B$6,"n/a")</f>
-        <v>618.312595065672</v>
+        <v>612.414841490598</v>
       </c>
       <c r="C83" s="8" t="n">
         <f aca="false">IF(C82&gt;$L39,(SUMPRODUCT($B46:$K46/(1+C82)^$B$16:$K$16)+$L46/(C82-$L39)/(1+C82)^$K$16+$B$7+$B$8)/$B$6,"n/a")</f>
-        <v>303.331295200872</v>
+        <v>299.861167615275</v>
       </c>
       <c r="D83" s="8" t="n">
         <f aca="false">IF(D82&gt;$L39,(SUMPRODUCT($B46:$K46/(1+D82)^$B$16:$K$16)+$L46/(D82-$L39)/(1+D82)^$K$16+$B$7+$B$8)/$B$6,"n/a")</f>
-        <v>198.527621986931</v>
+        <v>195.865253945905</v>
       </c>
       <c r="E83" s="8" t="n">
         <f aca="false">IF(E82&gt;$L39,(SUMPRODUCT($B46:$K46/(1+E82)^$B$16:$K$16)+$L46/(E82-$L39)/(1+E82)^$K$16+$B$7+$B$8)/$B$6,"n/a")</f>
-        <v>146.258709049454</v>
+        <v>143.999208038025</v>
       </c>
       <c r="F83" s="8" t="n">
         <f aca="false">IF(F82&gt;$L39,(SUMPRODUCT($B46:$K46/(1+F82)^$B$16:$K$16)+$L46/(F82-$L39)/(1+F82)^$K$16+$B$7+$B$8)/$B$6,"n/a")</f>
-        <v>114.996601171465</v>
+        <v>112.978064703314</v>
       </c>
       <c r="G83" s="8" t="n">
         <f aca="false">IF(G82&gt;$L39,(SUMPRODUCT($B46:$K46/(1+G82)^$B$16:$K$16)+$L46/(G82-$L39)/(1+G82)^$K$16+$B$7+$B$8)/$B$6,"n/a")</f>
-        <v>94.2324479617951</v>
+        <v>92.3739666246706</v>
       </c>
       <c r="H83" s="8" t="n">
         <f aca="false">IF(H82&gt;$L39,(SUMPRODUCT($B46:$K46/(1+H82)^$B$16:$K$16)+$L46/(H82-$L39)/(1+H82)^$K$16+$B$7+$B$8)/$B$6,"n/a")</f>
-        <v>79.4628213320494</v>
+        <v>77.7181942225764</v>
       </c>
       <c r="I83" s="8" t="n">
         <f aca="false">IF(I82&gt;$L39,(SUMPRODUCT($B46:$K46/(1+I82)^$B$16:$K$16)+$L46/(I82-$L39)/(1+I82)^$K$16+$B$7+$B$8)/$B$6,"n/a")</f>
-        <v>68.4362980512501</v>
+        <v>66.776676282547</v>
       </c>
       <c r="J83" s="8" t="n">
         <f aca="false">IF(J82&gt;$L39,(SUMPRODUCT($B46:$K46/(1+J82)^$B$16:$K$16)+$L46/(J82-$L39)/(1+J82)^$K$16+$B$7+$B$8)/$B$6,"n/a")</f>
-        <v>59.9023231172952</v>
+        <v>58.3084959981097</v>
       </c>
       <c r="K83" s="8" t="n">
         <f aca="false">IF(K82&gt;$L39,(SUMPRODUCT($B46:$K46/(1+K82)^$B$16:$K$16)+$L46/(K82-$L39)/(1+K82)^$K$16+$B$7+$B$8)/$B$6,"n/a")</f>
-        <v>53.1107571264277</v>
+        <v>51.5692953933111</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B84" s="7" t="n">
         <f aca="false">IFERROR(B83/$B$4-1,"n/a")</f>
-        <v>2.94231442913588</v>
+        <v>3.07923027703056</v>
       </c>
       <c r="C84" s="7" t="n">
         <f aca="false">IFERROR(C83/$B$4-1,"n/a")</f>
-        <v>0.934017439434276</v>
+        <v>0.997343419804666</v>
       </c>
       <c r="D84" s="7" t="n">
         <f aca="false">IFERROR(D83/$B$4-1,"n/a")</f>
-        <v>0.265797130750646</v>
+        <v>0.304637673655533</v>
       </c>
       <c r="E84" s="7" t="n">
         <f aca="false">IFERROR(E83/$B$4-1,"n/a")</f>
-        <v>-0.0674655123090162</v>
+        <v>-0.0408365547323984</v>
       </c>
       <c r="F84" s="7" t="n">
         <f aca="false">IFERROR(F83/$B$4-1,"n/a")</f>
-        <v>-0.266790352132973</v>
+        <v>-0.247465098892201</v>
       </c>
       <c r="G84" s="7" t="n">
         <f aca="false">IFERROR(G83/$B$4-1,"n/a")</f>
-        <v>-0.399181025492253</v>
+        <v>-0.384706809933587</v>
       </c>
       <c r="H84" s="7" t="n">
         <f aca="false">IFERROR(H83/$B$4-1,"n/a")</f>
-        <v>-0.493351049910422</v>
+        <v>-0.482327354808657</v>
       </c>
       <c r="I84" s="7" t="n">
         <f aca="false">IFERROR(I83/$B$4-1,"n/a")</f>
-        <v>-0.563655329946123</v>
+        <v>-0.555207644824173</v>
       </c>
       <c r="J84" s="7" t="n">
         <f aca="false">IFERROR(J83/$B$4-1,"n/a")</f>
-        <v>-0.618067309887177</v>
+        <v>-0.611613295156799</v>
       </c>
       <c r="K84" s="7" t="n">
         <f aca="false">IFERROR(K83/$B$4-1,"n/a")</f>
-        <v>-0.661369821943205</v>
+        <v>-0.656502395301998</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B86" s="26" t="n">
         <f aca="false">IFERROR(IF(MATCH($B$4,$B$83:$K$83,-1)=10,"above 14%",INDEX($B$82:$K$82,MATCH($B$4,$B$83:$K$83,-1))+(INDEX($B$83:$K$83,MATCH($B$4,$B$83:$K$83,-1))-$B$4)/(INDEX($B$83:$K$83,MATCH($B$4,$B$83:$K$83,-1))-INDEX($B$83:$K$83,MATCH($B$4,$B$83:$K$83,-1)+1))*(INDEX($B$82:$K$82,MATCH($B$4,$B$83:$K$83,-1)+1)-INDEX($B$82:$K$82,MATCH($B$4,$B$83:$K$83,-1)))),"below 5%")</f>
-        <v>0.0779756053156868</v>
+        <v>0.0788179565543007</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -3312,163 +3303,163 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B5" s="16" t="n">
         <v>2</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B6" s="16" t="n">
         <v>2</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B7" s="14" t="n">
         <v>0.0503</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B8" s="14" t="n">
         <v>0.05</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B9" s="14" t="n">
         <v>0.012</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="B12" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="B12" s="18" t="s">
+      <c r="C12" s="18" t="s">
         <v>98</v>
-      </c>
-      <c r="C12" s="18" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B13" s="27" t="n">
         <v>0.99</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B14" s="28"/>
       <c r="C14" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B15" s="28" t="n">
         <f aca="false">0.67*IF(ISNUMBER(B14),B14,B13)+0.33</f>
         <v>0.9933</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B16" s="28" t="n">
         <f aca="false">IF($B$6=1,IF(ISNUMBER(B14),B14,B13),B15)</f>
         <v>0.9933</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B17" s="25" t="n">
         <f aca="false">$B$7+B16*$B$8</f>
         <v>0.099965</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B18" s="25" t="n">
         <f aca="false">$B$7+$B$9</f>
         <v>0.0623</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B19" s="6" t="n">
         <f aca="false">NOW!B9</f>
         <v>0.2</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B20" s="25" t="n">
         <f aca="false">B18*(1-B19)</f>
@@ -3478,85 +3469,85 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B21" s="29" t="n">
         <f aca="false">NOW!B4*NOW!B6</f>
-        <v>161.5452</v>
+        <v>155.83494</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B22" s="30" t="n">
+        <v>7.52</v>
+      </c>
+      <c r="C22" s="3" t="s">
         <v>115</v>
-      </c>
-      <c r="B22" s="30" t="n">
-        <v>8.45</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B23" s="25" t="n">
         <f aca="false">B21/(B21+B22)</f>
-        <v>0.950292714147223</v>
+        <v>0.953965273410158</v>
       </c>
       <c r="C23" s="3"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B24" s="25" t="n">
         <f aca="false">B22/(B21+B22)</f>
-        <v>0.049707285852777</v>
+        <v>0.0460347265898417</v>
       </c>
       <c r="C24" s="3"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B25" s="25" t="n">
         <f aca="false">B23*B17+B24*B20</f>
-        <v>0.0974734222966296</v>
+        <v>0.0976575093296842</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B26" s="31" t="n">
         <v>0.0922</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B27" s="26" t="n">
         <f aca="false">IF($B$5=1,B25,B26)</f>
         <v>0.0922</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B28" s="1" t="str">
         <f aca="false">IF(B27&gt;MAX(NOW!L21,NOW!L39,NOW!L57),"OK","WACC must exceed growth")</f>
@@ -3566,14 +3557,14 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B29" s="25" t="n">
         <f aca="false">B27</f>
         <v>0.0922</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>
